--- a/Result/profitability/3228.xlsx
+++ b/Result/profitability/3228.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.21</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.48</v>
+        <v>-0.47125</v>
       </c>
       <c r="N2" t="n">
-        <v>60.19375</v>
+        <v>59.74625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.36</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.37</v>
+        <v>-0.36</v>
       </c>
       <c r="N3" t="n">
-        <v>58.8625</v>
+        <v>58.42125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,16 +899,16 @@
         <v>0.15</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.285</v>
+        <v>-0.28</v>
       </c>
       <c r="N4" t="n">
-        <v>57.4</v>
+        <v>56.56625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.26</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.25625</v>
+        <v>-0.2375</v>
       </c>
       <c r="N5" t="n">
-        <v>56.04625</v>
+        <v>55.56874999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.76</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.27625</v>
+        <v>-0.28125</v>
       </c>
       <c r="N6" t="n">
-        <v>52.75125</v>
+        <v>52.455</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.13</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.24125</v>
+        <v>-0.23125</v>
       </c>
       <c r="N7" t="n">
-        <v>52.5825</v>
+        <v>52.67749999999999</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.16</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.155</v>
+        <v>-0.1425</v>
       </c>
       <c r="N8" t="n">
-        <v>52.82375</v>
+        <v>52.63375000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>-0.2375</v>
       </c>
       <c r="N9" t="n">
-        <v>51.11875000000001</v>
+        <v>51.11875</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>-0.275</v>
       </c>
       <c r="N10" t="n">
-        <v>53.025</v>
+        <v>53.02500000000001</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1772,7 +1772,7 @@
         <v>-0.05</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3262499999999999</v>
+        <v>-0.32625</v>
       </c>
       <c r="N11" t="n">
         <v>53.49625</v>
@@ -2029,7 +2029,7 @@
         <v>-0.45</v>
       </c>
       <c r="N13" t="n">
-        <v>54.21</v>
+        <v>54.20999999999999</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3228</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>96</v>
+      </c>
+      <c r="D75" t="n">
+        <v>39</v>
+      </c>
+      <c r="E75" t="n">
+        <v>57</v>
+      </c>
+      <c r="F75" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-32</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-33.11%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-32</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-32</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="N75" t="n">
+        <v>61.81125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1818181818181819</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.520000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.02502469542311492</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.82</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.06059644670050757</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
